--- a/univ_req1.xlsx
+++ b/univ_req1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\학교 업무\01. 수업자료, 교과서\00. 교과서(인공지능 수학 포함)\22개정 인공지능수학(공동)\보고서 예시안\과목 추천 AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70F1109-89E8-4031-8C12-96A4047D4259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C611C2-5196-4B88-8BD0-0393496B217C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="128">
   <si>
     <t>계열</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -348,42 +348,12 @@
     <t>화학, 생명과학</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">세포와 물질대사, 생물의 유전, 물질과 에너지 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>11111111</t>
-    </r>
-  </si>
-  <si>
     <t>약학과</t>
   </si>
   <si>
     <t>신약, 약물, 조제, 화학, 헬스케어, 제약, 바이오</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">물질과 에너지, 화학 반응의 세계, 세포와 물질대사 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2222</t>
-    </r>
-  </si>
-  <si>
     <t>간호학과</t>
   </si>
   <si>
@@ -393,21 +363,6 @@
     <t>생명과학</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">화학, 세포와 물질대사, 생물의 유전 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>3333</t>
-    </r>
-  </si>
-  <si>
     <t>수의예과</t>
   </si>
   <si>
@@ -417,21 +372,6 @@
     <t>생명과학, 화학</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">세포와 물질대사, 생물의 유전 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4444</t>
-    </r>
-  </si>
-  <si>
     <t>공학</t>
   </si>
   <si>
@@ -444,143 +384,1110 @@
     <t>대수, 미적분I</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">역학과 에너지, 전자기와 양자, 물질과 에너지 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>5555</t>
-    </r>
-  </si>
-  <si>
     <t>스마트보안학부</t>
   </si>
   <si>
-    <t>해킹, 암호, 사이버보안, 정보보호, 네트워크, 화이트해커</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- (수학적 논리력 중시) </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>6666</t>
-    </r>
-  </si>
-  <si>
     <t>자연</t>
   </si>
   <si>
     <t>지구환경과학과</t>
   </si>
   <si>
-    <t>기후, 대기, 지질, 오염, 탄소중립, 기상, 해양</t>
-  </si>
-  <si>
     <t>지구과학, 화학</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">지구시스템과학, 행성우주과학 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>7777</t>
-    </r>
-  </si>
-  <si>
     <t>화공생명공학과</t>
   </si>
   <si>
     <t>공정, 바이오, 플랜트, 에너지, 반응, 소재, 제약</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">물질과 에너지, 화학 반응의 세계, 세포와 물질대사 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>8888</t>
-    </r>
-  </si>
-  <si>
     <t>인문/사회</t>
   </si>
   <si>
     <t>경영학부</t>
   </si>
   <si>
-    <t>마케팅, 재무, 회계, 조직, CEO, 창업, 전략</t>
-  </si>
-  <si>
     <t>경제수학, 미적분II</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">- (사회 교과: 경제 권장) </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>9999</t>
-    </r>
-  </si>
-  <si>
     <t>경제학과</t>
   </si>
   <si>
-    <t>금융, 환율, 통계, 시장, 물가, 정책, 데이터분석</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- (사회 교과: 경제, 국제경제 권장) </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>10101010</t>
-    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세포와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물질대사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생물의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물질과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에너지</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물질과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에너지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반응의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세포와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물질대사</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세포와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물질대사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생물의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유전</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세포와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물질대사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생물의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유전</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>역학과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에너지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전자기와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물질과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에너지</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지구시스템과학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>행성우주과학</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경제, 국제경제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마케팅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조직</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, CEO, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>창업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전략</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>금융</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>환율</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정책</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해킹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>암호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사이버보안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보보호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>네트워크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화이트해커, 보안, 정보</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지질</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오염</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탄소중립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지구과학</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,11 +1522,25 @@
       <family val="2"/>
     </font>
     <font>
-      <vertAlign val="superscript"/>
-      <sz val="8"/>
-      <color rgb="FF444746"/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -657,7 +1578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -667,6 +1588,15 @@
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1572,7 +2502,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A32" s="2" t="s">
         <v>90</v>
       </c>
@@ -1591,19 +2521,19 @@
       <c r="F32" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G32" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A33" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>47</v>
@@ -1614,68 +2544,68 @@
       <c r="F33" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G33" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A34" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G34" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A35" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>44</v>
@@ -1683,19 +2613,19 @@
       <c r="F36" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G36" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>112</v>
+      <c r="C37" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>47</v>
@@ -1706,42 +2636,40 @@
       <c r="F37" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G38" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A39" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>47</v>
@@ -1752,18 +2680,18 @@
       <c r="F39" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G39" s="4" t="s">
-        <v>121</v>
+      <c r="G39" s="5" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A40" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>124</v>
       </c>
       <c r="D40" s="2" t="s">
@@ -1773,21 +2701,21 @@
         <v>40</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>126</v>
+        <v>114</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A41" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>47</v>
@@ -1796,10 +2724,10 @@
         <v>40</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>129</v>
+        <v>114</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/univ_req1.xlsx
+++ b/univ_req1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\학교 업무\01. 수업자료, 교과서\00. 교과서(인공지능 수학 포함)\22개정 인공지능수학(공동)\보고서 예시안\과목 추천 AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\내 드라이브\학교 업무\01. 수업자료, 교과서\00. 교과서(인공지능 수학 포함)\22개정 인공지능수학(공동)\보고서 및 수행평가 예시안\과목 추천 AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C611C2-5196-4B88-8BD0-0393496B217C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6A9F0F-F954-48E7-98CC-C56FEDC27D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,18 +183,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>대수, 미적분I, 확률과 통계, 미적분II, 기하</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>인공지능수학</t>
   </si>
   <si>
-    <t>대수, 미적분I, 확률과 통계, 미적분II</t>
-  </si>
-  <si>
     <t>기하</t>
   </si>
   <si>
@@ -207,12 +201,6 @@
     <t>물리학, 화학</t>
   </si>
   <si>
-    <t>대수, 미적분I, 확률과 통계</t>
-  </si>
-  <si>
-    <t>미적분II, 기하</t>
-  </si>
-  <si>
     <t>물리학, 역학과 에너지</t>
   </si>
   <si>
@@ -231,9 +219,6 @@
     <t>화학, 생명과학, 세포와 물질대사, 생물의 유전</t>
   </si>
   <si>
-    <t>미적분II</t>
-  </si>
-  <si>
     <t>물리학, 물질과 에너지, 화학 반응의 세계</t>
   </si>
   <si>
@@ -243,9 +228,6 @@
     <t>역학과 에너지, 물질과 에너지, 정보</t>
   </si>
   <si>
-    <t>기하, 미적분II</t>
-  </si>
-  <si>
     <t>수식, 증명, 통계, 금융, 암호, 데이터분석, 논리</t>
   </si>
   <si>
@@ -381,9 +363,6 @@
     <t>자율주행, 전기차, 드론, 배터리, 교통, 센서, AI</t>
   </si>
   <si>
-    <t>대수, 미적분I</t>
-  </si>
-  <si>
     <t>스마트보안학부</t>
   </si>
   <si>
@@ -408,9 +387,6 @@
     <t>경영학부</t>
   </si>
   <si>
-    <t>경제수학, 미적분II</t>
-  </si>
-  <si>
     <t>경제학과</t>
   </si>
   <si>
@@ -1481,13 +1457,37 @@
       <t>지구과학</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미적분2, 기하</t>
+  </si>
+  <si>
+    <t>미적분2</t>
+  </si>
+  <si>
+    <t>기하, 미적분2</t>
+  </si>
+  <si>
+    <t>경제수학, 미적분2</t>
+  </si>
+  <si>
+    <t>대수, 미적분1, 확률과 통계, 미적분2, 기하</t>
+  </si>
+  <si>
+    <t>대수, 미적분1, 확률과 통계, 미적분2</t>
+  </si>
+  <si>
+    <t>대수, 미적분1, 확률과 통계</t>
+  </si>
+  <si>
+    <t>대수, 미적분1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1542,6 +1542,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1578,7 +1585,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1599,6 +1606,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1922,10 +1930,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -1933,10 +1941,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -1947,19 +1955,19 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -1967,19 +1975,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -1987,19 +1995,19 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2007,19 +2015,19 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2027,19 +2035,19 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2047,19 +2055,19 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2067,19 +2075,19 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2087,19 +2095,19 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2107,19 +2115,19 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G12" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2127,19 +2135,19 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2147,19 +2155,19 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G14" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2167,19 +2175,19 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="F15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2187,19 +2195,19 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="F16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2207,19 +2215,19 @@
         <v>20</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2227,19 +2235,19 @@
         <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>42</v>
+        <v>70</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2247,19 +2255,19 @@
         <v>22</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2267,19 +2275,19 @@
         <v>23</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G20" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2287,19 +2295,19 @@
         <v>24</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G21" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2307,19 +2315,19 @@
         <v>25</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2327,19 +2335,19 @@
         <v>26</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2347,19 +2355,19 @@
         <v>27</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2367,19 +2375,19 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2387,19 +2395,19 @@
         <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2407,19 +2415,19 @@
         <v>30</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2427,19 +2435,19 @@
         <v>31</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2447,19 +2455,19 @@
         <v>32</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2467,19 +2475,19 @@
         <v>33</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2487,247 +2495,247 @@
         <v>34</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A32" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A33" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="C34" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A35" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A36" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A37" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C37" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="E37" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A39" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A40" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F40" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A41" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
